--- a/resultados_comparativos.xlsx
+++ b/resultados_comparativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNIVERSIDAD\SISTEMAS OPERATIVOS\concurrencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34568757-ACC8-4F18-9E7A-2BD859934F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CE22E6-2128-49D5-A461-7C6E4A8D50E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="23">
+  <futureMetadata name="XLRICHVALUE" count="34">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -188,8 +188,85 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="30"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="31"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="32"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="33"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="23">
+  <valueMetadata count="34">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -258,13 +335,46 @@
     </bk>
     <bk>
       <rc t="1" v="22"/>
+    </bk>
+    <bk>
+      <rc t="1" v="23"/>
+    </bk>
+    <bk>
+      <rc t="1" v="24"/>
+    </bk>
+    <bk>
+      <rc t="1" v="25"/>
+    </bk>
+    <bk>
+      <rc t="1" v="26"/>
+    </bk>
+    <bk>
+      <rc t="1" v="27"/>
+    </bk>
+    <bk>
+      <rc t="1" v="28"/>
+    </bk>
+    <bk>
+      <rc t="1" v="29"/>
+    </bk>
+    <bk>
+      <rc t="1" v="30"/>
+    </bk>
+    <bk>
+      <rc t="1" v="31"/>
+    </bk>
+    <bk>
+      <rc t="1" v="32"/>
+    </bk>
+    <bk>
+      <rc t="1" v="33"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
   <si>
     <t xml:space="preserve">Métrica </t>
   </si>
@@ -504,12 +614,18 @@
   <si>
     <t>115 </t>
   </si>
+  <si>
+    <t>Tiempos de espera con Starvation</t>
+  </si>
+  <si>
+    <t>Tiempos de espera sin Starvation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -561,6 +677,14 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -784,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -857,6 +981,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -916,7 +1052,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="23">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="34">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1007,6 +1143,50 @@
   </rv>
   <rv s="0">
     <v>22</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>23</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>24</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>25</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>26</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>27</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>28</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>29</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>30</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>31</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>32</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>33</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1046,6 +1226,17 @@
   <rel r:id="rId21"/>
   <rel r:id="rId22"/>
   <rel r:id="rId23"/>
+  <rel r:id="rId24"/>
+  <rel r:id="rId25"/>
+  <rel r:id="rId26"/>
+  <rel r:id="rId27"/>
+  <rel r:id="rId28"/>
+  <rel r:id="rId29"/>
+  <rel r:id="rId30"/>
+  <rel r:id="rId31"/>
+  <rel r:id="rId32"/>
+  <rel r:id="rId33"/>
+  <rel r:id="rId34"/>
 </richValueRels>
 </file>
 
@@ -1334,7 +1525,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:G23"/>
+  <dimension ref="B1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.5546875" customWidth="1"/>
@@ -1345,11 +1536,11 @@
     <col min="7" max="7" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:7" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:7" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:7" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:12" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:12" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:12" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="2:12" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
         <v>46</v>
       </c>
@@ -1358,9 +1549,14 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
-    </row>
-    <row r="6" spans="2:7" ht="13.2" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+    </row>
+    <row r="6" spans="2:12" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
@@ -1379,8 +1575,13 @@
       <c r="G7" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" ht="61.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="29" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+    </row>
+    <row r="8" spans="2:12" ht="61.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="27">
         <v>2</v>
       </c>
@@ -1396,11 +1597,14 @@
       <c r="F8" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="28" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="61.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="28" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+    </row>
+    <row r="9" spans="2:12" ht="61.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27">
         <v>4</v>
       </c>
@@ -1416,9 +1620,14 @@
       <c r="F9" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="28"/>
-    </row>
-    <row r="10" spans="2:7" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="28" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+    </row>
+    <row r="10" spans="2:12" ht="73.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="27">
         <v>6</v>
       </c>
@@ -1434,9 +1643,11 @@
       <c r="F10" s="24">
         <v>19</v>
       </c>
-      <c r="G10" s="28"/>
-    </row>
-    <row r="11" spans="2:7" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="28" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="76.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="27">
         <v>8</v>
       </c>
@@ -1452,9 +1663,11 @@
       <c r="F11" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="28"/>
-    </row>
-    <row r="12" spans="2:7" ht="80.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="28" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="80.400000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="27">
         <v>10</v>
       </c>
@@ -1470,9 +1683,11 @@
       <c r="F12" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="28"/>
-    </row>
-    <row r="16" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="28" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>47</v>
       </c>
@@ -1481,8 +1696,13 @@
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
-    </row>
-    <row r="18" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+    </row>
+    <row r="18" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="11" t="s">
         <v>13</v>
       </c>
@@ -1501,8 +1721,13 @@
       <c r="G18" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="32" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+    </row>
+    <row r="19" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="7">
         <v>2</v>
       </c>
@@ -1518,9 +1743,14 @@
       <c r="F19" s="24">
         <v>20</v>
       </c>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="8" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+    </row>
+    <row r="20" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="7">
         <v>4</v>
       </c>
@@ -1536,9 +1766,14 @@
       <c r="F20" s="24">
         <v>20</v>
       </c>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="8" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+    </row>
+    <row r="21" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="7">
         <v>6</v>
       </c>
@@ -1554,9 +1789,14 @@
       <c r="F21" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="8" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+    </row>
+    <row r="22" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="7">
         <v>8</v>
       </c>
@@ -1572,9 +1812,14 @@
       <c r="F22" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="8" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+    </row>
+    <row r="23" spans="2:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="7">
         <v>10</v>
       </c>
@@ -1590,12 +1835,18 @@
       <c r="F23" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="8"/>
+      <c r="G23" s="8" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="J18:L22"/>
+    <mergeCell ref="J7:L9"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B16:G16"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J16:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1645,7 +1896,7 @@
       <c r="D2" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="1" t="e" vm="4">
+      <c r="E2" s="1" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1662,7 +1913,7 @@
       <c r="D3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="1" t="e" vm="5">
+      <c r="E3" s="1" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1679,7 +1930,7 @@
       <c r="D4" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="1" t="e" vm="6">
+      <c r="E4" s="1" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1696,7 +1947,7 @@
       <c r="D5" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="1" t="e" vm="7">
+      <c r="E5" s="1" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1713,7 +1964,7 @@
       <c r="D6" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="1" t="e" vm="8">
+      <c r="E6" s="1" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1730,7 +1981,7 @@
       <c r="D7" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="1" t="e" vm="9">
+      <c r="E7" s="1" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1747,7 +1998,7 @@
       <c r="D8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="1" t="e" vm="10">
+      <c r="E8" s="1" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1764,7 +2015,7 @@
       <c r="D9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="1" t="e" vm="11">
+      <c r="E9" s="1" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1781,7 +2032,7 @@
       <c r="D10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="1" t="e" vm="12">
+      <c r="E10" s="1" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1798,7 +2049,7 @@
       <c r="D11" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="1" t="e" vm="13">
+      <c r="E11" s="1" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1815,7 +2066,7 @@
       <c r="D12" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="1" t="e" vm="14">
+      <c r="E12" s="1" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1832,7 +2083,7 @@
       <c r="D13" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="1" t="e" vm="15">
+      <c r="E13" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1849,7 +2100,7 @@
       <c r="D14" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="1" t="e" vm="16">
+      <c r="E14" s="1" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1866,7 +2117,7 @@
       <c r="D15" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="1" t="e" vm="17">
+      <c r="E15" s="1" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1883,7 +2134,7 @@
       <c r="D16" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="1" t="e" vm="18">
+      <c r="E16" s="1" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1900,7 +2151,7 @@
       <c r="D17" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="1" t="e" vm="19">
+      <c r="E17" s="1" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1917,7 +2168,7 @@
       <c r="D18" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="1" t="e" vm="20">
+      <c r="E18" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1934,7 +2185,7 @@
       <c r="D19" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="1" t="e" vm="21">
+      <c r="E19" s="1" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1951,7 +2202,7 @@
       <c r="D20" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="1" t="e" vm="22">
+      <c r="E20" s="1" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1968,7 +2219,7 @@
       <c r="D21" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="1" t="e" vm="23">
+      <c r="E21" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
     </row>
